--- a/pa-temp-fix-system.com/php/shell/sp/negativeTarget/excel/M6精准否定asin.xlsx
+++ b/pa-temp-fix-system.com/php/shell/sp/negativeTarget/excel/M6精准否定asin.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="411">
   <si>
     <t>channel</t>
   </si>
@@ -38,13 +38,13 @@
     <t>seller_id</t>
   </si>
   <si>
+    <t>campaign_id</t>
+  </si>
+  <si>
     <t>ad_group_id</t>
   </si>
   <si>
-    <t>search_term-可直接复制</t>
-  </si>
-  <si>
-    <t>否定类型</t>
+    <t>keywordtext</t>
   </si>
   <si>
     <t>amazon_us</t>
@@ -53,6 +53,9 @@
     <t>amazon_us_moto</t>
   </si>
   <si>
+    <t>461183700300026</t>
+  </si>
+  <si>
     <t>286517451552894</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>amazon_us_find</t>
   </si>
   <si>
+    <t>352268674941412</t>
+  </si>
+  <si>
     <t>509467505415244</t>
   </si>
   <si>
@@ -74,6 +80,9 @@
     <t>amazon_ca_moto</t>
   </si>
   <si>
+    <t>345404633496328</t>
+  </si>
+  <si>
     <t>547157499874643</t>
   </si>
   <si>
@@ -83,6 +92,9 @@
     <t>amazon_ca_piccocasa</t>
   </si>
   <si>
+    <t>506878034770612</t>
+  </si>
+  <si>
     <t>288653444570764</t>
   </si>
   <si>
@@ -92,6 +104,9 @@
     <t>amazon</t>
   </si>
   <si>
+    <t>291546772827791</t>
+  </si>
+  <si>
     <t>555540364637531</t>
   </si>
   <si>
@@ -104,12 +119,18 @@
     <t>amazon_ca_sopro</t>
   </si>
   <si>
+    <t>547830866698806</t>
+  </si>
+  <si>
     <t>508199701925174</t>
   </si>
   <si>
     <t>B091TPFN33</t>
   </si>
   <si>
+    <t>385860187642257</t>
+  </si>
+  <si>
     <t>399201953159522</t>
   </si>
   <si>
@@ -119,12 +140,18 @@
     <t>B07NQ13B9C</t>
   </si>
   <si>
+    <t>297562789781569</t>
+  </si>
+  <si>
     <t>302289815589494</t>
   </si>
   <si>
     <t>B0GK2J6FFM</t>
   </si>
   <si>
+    <t>71170624242798</t>
+  </si>
+  <si>
     <t>476123752912135</t>
   </si>
   <si>
@@ -134,6 +161,9 @@
     <t>amazon_ca_tuc</t>
   </si>
   <si>
+    <t>35075741069046</t>
+  </si>
+  <si>
     <t>381325345820272</t>
   </si>
   <si>
@@ -146,12 +176,18 @@
     <t>B0F7HHF64S</t>
   </si>
   <si>
+    <t>295014882707046</t>
+  </si>
+  <si>
     <t>482750404959956</t>
   </si>
   <si>
     <t>B0D33YM53K</t>
   </si>
   <si>
+    <t>492566110872029</t>
+  </si>
+  <si>
     <t>420914796157558</t>
   </si>
   <si>
@@ -161,18 +197,27 @@
     <t>amazon_ca_tuto</t>
   </si>
   <si>
+    <t>144229850589661</t>
+  </si>
+  <si>
     <t>340337223236501</t>
   </si>
   <si>
     <t>B0019LZZUE</t>
   </si>
   <si>
+    <t>346515290823917</t>
+  </si>
+  <si>
     <t>446467112625286</t>
   </si>
   <si>
     <t>B073Y3K7ZQ</t>
   </si>
   <si>
+    <t>156215289065954</t>
+  </si>
+  <si>
     <t>115451160999978</t>
   </si>
   <si>
@@ -182,6 +227,9 @@
     <t>amazon_ca_rock</t>
   </si>
   <si>
+    <t>509905558365112</t>
+  </si>
+  <si>
     <t>451602371140694</t>
   </si>
   <si>
@@ -191,12 +239,18 @@
     <t>amazon_ca_ac1</t>
   </si>
   <si>
+    <t>376067929241553</t>
+  </si>
+  <si>
     <t>288350067620778</t>
   </si>
   <si>
     <t>B08253ZXRC</t>
   </si>
   <si>
+    <t>267573139609085</t>
+  </si>
+  <si>
     <t>300434839985094</t>
   </si>
   <si>
@@ -206,6 +260,9 @@
     <t>amazon_us_rrc</t>
   </si>
   <si>
+    <t>427538128015695</t>
+  </si>
+  <si>
     <t>505464669674034</t>
   </si>
   <si>
@@ -218,6 +275,9 @@
     <t>amazon_uk_rrc</t>
   </si>
   <si>
+    <t>472812128274272</t>
+  </si>
+  <si>
     <t>341860488208906</t>
   </si>
   <si>
@@ -227,6 +287,9 @@
     <t>amazon_us_ac1</t>
   </si>
   <si>
+    <t>452058750111002</t>
+  </si>
+  <si>
     <t>432815665803446</t>
   </si>
   <si>
@@ -236,6 +299,9 @@
     <t>B0CTX26MYJ</t>
   </si>
   <si>
+    <t>202909207224057</t>
+  </si>
+  <si>
     <t>412333939726355</t>
   </si>
   <si>
@@ -245,12 +311,18 @@
     <t>amazon_uk_moto</t>
   </si>
   <si>
+    <t>323067021946769</t>
+  </si>
+  <si>
     <t>431948212093907</t>
   </si>
   <si>
     <t>B07WW7K2P3</t>
   </si>
   <si>
+    <t>465922743621704</t>
+  </si>
+  <si>
     <t>460551703449890</t>
   </si>
   <si>
@@ -260,12 +332,18 @@
     <t>amazon_us_tuc</t>
   </si>
   <si>
+    <t>473073327410316</t>
+  </si>
+  <si>
     <t>363851636405740</t>
   </si>
   <si>
     <t>B0DHCMB8SM</t>
   </si>
   <si>
+    <t>514753641173224</t>
+  </si>
+  <si>
     <t>303875022914067</t>
   </si>
   <si>
@@ -281,12 +359,18 @@
     <t>B0CT29FF4D</t>
   </si>
   <si>
+    <t>311915438639568</t>
+  </si>
+  <si>
     <t>437885275122640</t>
   </si>
   <si>
     <t>B0FPQWJ8JH</t>
   </si>
   <si>
+    <t>378820404898285</t>
+  </si>
+  <si>
     <t>524765628937402</t>
   </si>
   <si>
@@ -296,6 +380,9 @@
     <t>amazon_us_ifn</t>
   </si>
   <si>
+    <t>555300182457874</t>
+  </si>
+  <si>
     <t>538810796829808</t>
   </si>
   <si>
@@ -308,18 +395,27 @@
     <t>amazon_us_sopro</t>
   </si>
   <si>
+    <t>181102524850224</t>
+  </si>
+  <si>
     <t>349457739946782</t>
   </si>
   <si>
     <t>B0CWRTQ429</t>
   </si>
   <si>
+    <t>214198698073795</t>
+  </si>
+  <si>
     <t>187202378670633</t>
   </si>
   <si>
     <t>B0DSG3YNZJ</t>
   </si>
   <si>
+    <t>103503896302759</t>
+  </si>
+  <si>
     <t>519939849960791</t>
   </si>
   <si>
@@ -335,12 +431,18 @@
     <t>amazon_uk2</t>
   </si>
   <si>
+    <t>350655043236583</t>
+  </si>
+  <si>
     <t>353593777608896</t>
   </si>
   <si>
     <t>B0C5CPT9QQ</t>
   </si>
   <si>
+    <t>516078975126877</t>
+  </si>
+  <si>
     <t>326683897722498</t>
   </si>
   <si>
@@ -350,6 +452,9 @@
     <t>B084Q997R5</t>
   </si>
   <si>
+    <t>390221061346970</t>
+  </si>
+  <si>
     <t>430035225427042</t>
   </si>
   <si>
@@ -362,12 +467,18 @@
     <t>B01HG92NES</t>
   </si>
   <si>
+    <t>351170575702872</t>
+  </si>
+  <si>
     <t>466878568299150</t>
   </si>
   <si>
     <t>B01MSLVPLQ</t>
   </si>
   <si>
+    <t>447247027930351</t>
+  </si>
+  <si>
     <t>543335739335095</t>
   </si>
   <si>
@@ -377,12 +488,18 @@
     <t>amazon_us_tuto</t>
   </si>
   <si>
+    <t>329368030538652</t>
+  </si>
+  <si>
     <t>485015835298255</t>
   </si>
   <si>
     <t>B0FB37QC75</t>
   </si>
   <si>
+    <t>417450498293859</t>
+  </si>
+  <si>
     <t>308752384278625</t>
   </si>
   <si>
@@ -392,6 +509,9 @@
     <t>B0B1L9BMG3</t>
   </si>
   <si>
+    <t>292807243243583</t>
+  </si>
+  <si>
     <t>502314095766792</t>
   </si>
   <si>
@@ -419,18 +539,27 @@
     <t>amazon_us_luux</t>
   </si>
   <si>
+    <t>357444881120538</t>
+  </si>
+  <si>
     <t>299398320944733</t>
   </si>
   <si>
     <t>B0F1YM7VQS</t>
   </si>
   <si>
+    <t>467788458449608</t>
+  </si>
+  <si>
     <t>331494688929368</t>
   </si>
   <si>
     <t>B0057MNSYQ</t>
   </si>
   <si>
+    <t>476047509797566</t>
+  </si>
+  <si>
     <t>483533182516893</t>
   </si>
   <si>
@@ -440,6 +569,9 @@
     <t>amazon_ca_ifn</t>
   </si>
   <si>
+    <t>553506146507203</t>
+  </si>
+  <si>
     <t>525949651149840</t>
   </si>
   <si>
@@ -452,12 +584,18 @@
     <t>amazon_ca_rrc</t>
   </si>
   <si>
+    <t>547995951916743</t>
+  </si>
+  <si>
     <t>318714436415466</t>
   </si>
   <si>
     <t>B09G6SNDYP</t>
   </si>
   <si>
+    <t>289153361171720</t>
+  </si>
+  <si>
     <t>509364062342283</t>
   </si>
   <si>
@@ -467,6 +605,9 @@
     <t>amazon_ca_hood</t>
   </si>
   <si>
+    <t>497559735682457</t>
+  </si>
+  <si>
     <t>486302748706847</t>
   </si>
   <si>
@@ -482,24 +623,36 @@
     <t>amazon_ca_hero</t>
   </si>
   <si>
+    <t>7473970621524</t>
+  </si>
+  <si>
     <t>445938521136088</t>
   </si>
   <si>
     <t>B09J4CTYVS</t>
   </si>
   <si>
+    <t>67757896408534</t>
+  </si>
+  <si>
     <t>312123458408746</t>
   </si>
   <si>
     <t>amazon_ca_luux</t>
   </si>
   <si>
+    <t>341213557543751</t>
+  </si>
+  <si>
     <t>413247533466679</t>
   </si>
   <si>
     <t>B0D66ZKR9C</t>
   </si>
   <si>
+    <t>283205981538833</t>
+  </si>
+  <si>
     <t>292145596756142</t>
   </si>
   <si>
@@ -509,6 +662,9 @@
     <t>amazon_uk_sopro</t>
   </si>
   <si>
+    <t>236749242415101</t>
+  </si>
+  <si>
     <t>431283061551881</t>
   </si>
   <si>
@@ -518,6 +674,9 @@
     <t>B0CWL4PYQQ</t>
   </si>
   <si>
+    <t>131494784731465</t>
+  </si>
+  <si>
     <t>51557465334438</t>
   </si>
   <si>
@@ -527,12 +686,18 @@
     <t>B0DJT2LJTZ</t>
   </si>
   <si>
+    <t>306091798359033</t>
+  </si>
+  <si>
     <t>408271408666097</t>
   </si>
   <si>
     <t>B0CRDZDSHP</t>
   </si>
   <si>
+    <t>47492484827620</t>
+  </si>
+  <si>
     <t>339021860552615</t>
   </si>
   <si>
@@ -542,24 +707,36 @@
     <t>amazon_ca_find</t>
   </si>
   <si>
+    <t>377491789428788</t>
+  </si>
+  <si>
     <t>422466907102347</t>
   </si>
   <si>
     <t>B0B4RWGHMR</t>
   </si>
   <si>
+    <t>211291959587978</t>
+  </si>
+  <si>
     <t>805874479658</t>
   </si>
   <si>
     <t>B0BV2GQMSG</t>
   </si>
   <si>
+    <t>455508989046900</t>
+  </si>
+  <si>
     <t>388242359364089</t>
   </si>
   <si>
     <t>B0946JL8LX</t>
   </si>
   <si>
+    <t>241427124588441</t>
+  </si>
+  <si>
     <t>353630698057373</t>
   </si>
   <si>
@@ -578,6 +755,9 @@
     <t>B0BNPZZ71X</t>
   </si>
   <si>
+    <t>418924643910028</t>
+  </si>
+  <si>
     <t>463735024267472</t>
   </si>
   <si>
@@ -593,6 +773,9 @@
     <t>amazon_us_hero</t>
   </si>
   <si>
+    <t>216598803192386</t>
+  </si>
+  <si>
     <t>348916507277466</t>
   </si>
   <si>
@@ -602,12 +785,18 @@
     <t>B0FKBWP3SQ</t>
   </si>
   <si>
+    <t>540276522837502</t>
+  </si>
+  <si>
     <t>556543049689881</t>
   </si>
   <si>
     <t>B0FX3Y3NRH</t>
   </si>
   <si>
+    <t>530101266977097</t>
+  </si>
+  <si>
     <t>316003268033230</t>
   </si>
   <si>
@@ -620,6 +809,9 @@
     <t>B0CQYCJRXC</t>
   </si>
   <si>
+    <t>510435341201439</t>
+  </si>
+  <si>
     <t>466270835989181</t>
   </si>
   <si>
@@ -641,6 +833,9 @@
     <t>B0DTHFQNRX</t>
   </si>
   <si>
+    <t>515137987446415</t>
+  </si>
+  <si>
     <t>282472188496340</t>
   </si>
   <si>
@@ -650,12 +845,18 @@
     <t>B0FV2HFK8W</t>
   </si>
   <si>
+    <t>46421814849898</t>
+  </si>
+  <si>
     <t>457529581294000</t>
   </si>
   <si>
     <t>B0BZXWHYZH</t>
   </si>
   <si>
+    <t>398046904124854</t>
+  </si>
+  <si>
     <t>389205647574360</t>
   </si>
   <si>
@@ -686,6 +887,9 @@
     <t>B07BGVYDYJ</t>
   </si>
   <si>
+    <t>522264127051139</t>
+  </si>
+  <si>
     <t>440327160597674</t>
   </si>
   <si>
@@ -701,6 +905,9 @@
     <t>B078XCH1Q5</t>
   </si>
   <si>
+    <t>353577119986739</t>
+  </si>
+  <si>
     <t>297822154597369</t>
   </si>
   <si>
@@ -716,6 +923,9 @@
     <t>B0BC4GKPCZ</t>
   </si>
   <si>
+    <t>405249054918284</t>
+  </si>
+  <si>
     <t>391794718144837</t>
   </si>
   <si>
@@ -728,6 +938,9 @@
     <t>B0G6BTFGHH</t>
   </si>
   <si>
+    <t>442875543150054</t>
+  </si>
+  <si>
     <t>348256865853309</t>
   </si>
   <si>
@@ -740,24 +953,36 @@
     <t>B078WYHXNH</t>
   </si>
   <si>
+    <t>518191475003025</t>
+  </si>
+  <si>
     <t>481011455460057</t>
   </si>
   <si>
     <t>B08V5KYVHS</t>
   </si>
   <si>
+    <t>291912040071805</t>
+  </si>
+  <si>
     <t>324142398292009</t>
   </si>
   <si>
     <t>B09VC4PC9W</t>
   </si>
   <si>
+    <t>503996628684680</t>
+  </si>
+  <si>
     <t>335201553003969</t>
   </si>
   <si>
     <t>B00859W3DA</t>
   </si>
   <si>
+    <t>487990207684387</t>
+  </si>
+  <si>
     <t>544547555902652</t>
   </si>
   <si>
@@ -770,6 +995,9 @@
     <t>B0FPM4MCB9</t>
   </si>
   <si>
+    <t>469987748263357</t>
+  </si>
+  <si>
     <t>367901347652232</t>
   </si>
   <si>
@@ -779,6 +1007,9 @@
     <t>B07ZRZ99BL</t>
   </si>
   <si>
+    <t>455144575538610</t>
+  </si>
+  <si>
     <t>403942033015558</t>
   </si>
   <si>
@@ -794,6 +1025,9 @@
     <t>B004Z1239G</t>
   </si>
   <si>
+    <t>91092843820548</t>
+  </si>
+  <si>
     <t>305994079010074</t>
   </si>
   <si>
@@ -806,6 +1040,9 @@
     <t>amazon_us_rock</t>
   </si>
   <si>
+    <t>366555246406134</t>
+  </si>
+  <si>
     <t>341592850085084</t>
   </si>
   <si>
@@ -815,12 +1052,18 @@
     <t>B01HUUVZDS</t>
   </si>
   <si>
+    <t>231807215744652</t>
+  </si>
+  <si>
     <t>22367197552754</t>
   </si>
   <si>
     <t>B0B6181QSK</t>
   </si>
   <si>
+    <t>486785890078369</t>
+  </si>
+  <si>
     <t>562445463063491</t>
   </si>
   <si>
@@ -848,12 +1091,18 @@
     <t>B0DHRP2FFL</t>
   </si>
   <si>
+    <t>235210957195399</t>
+  </si>
+  <si>
     <t>510522459193169</t>
   </si>
   <si>
     <t>B0DTHSJFMY</t>
   </si>
   <si>
+    <t>500649909153348</t>
+  </si>
+  <si>
     <t>532132815500349</t>
   </si>
   <si>
@@ -863,6 +1112,9 @@
     <t>B08VNJM5QY</t>
   </si>
   <si>
+    <t>377799794197678</t>
+  </si>
+  <si>
     <t>486784793343794</t>
   </si>
   <si>
@@ -875,6 +1127,9 @@
     <t>B09Y46KSG1</t>
   </si>
   <si>
+    <t>482001821971850</t>
+  </si>
+  <si>
     <t>435798435201182</t>
   </si>
   <si>
@@ -884,6 +1139,9 @@
     <t>B09Y1HLFRP</t>
   </si>
   <si>
+    <t>376412806747710</t>
+  </si>
+  <si>
     <t>479086139603465</t>
   </si>
   <si>
@@ -908,6 +1166,9 @@
     <t>B0FDG8C9RH</t>
   </si>
   <si>
+    <t>339840993251599</t>
+  </si>
+  <si>
     <t>444049817882361</t>
   </si>
   <si>
@@ -926,6 +1187,9 @@
     <t>B09FXTPPLX</t>
   </si>
   <si>
+    <t>346018461005209</t>
+  </si>
+  <si>
     <t>313368928531605</t>
   </si>
   <si>
@@ -953,12 +1217,18 @@
     <t>B092LMZQZ9</t>
   </si>
   <si>
+    <t>460263301010643</t>
+  </si>
+  <si>
     <t>546569856562983</t>
   </si>
   <si>
     <t>B0DJZHMH7C</t>
   </si>
   <si>
+    <t>48372025748194</t>
+  </si>
+  <si>
     <t>407315878426468</t>
   </si>
   <si>
@@ -971,10 +1241,16 @@
     <t>B0D16LRCNX</t>
   </si>
   <si>
+    <t>357239611035729</t>
+  </si>
+  <si>
     <t>453431323438038</t>
   </si>
   <si>
     <t>B074STNQBQ</t>
+  </si>
+  <si>
+    <t>533952575522198</t>
   </si>
   <si>
     <t>379074846954426</t>
@@ -1152,7 +1428,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1162,12 +1438,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1490,7 +1760,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1514,16 +1784,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1532,89 +1802,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1622,9 +1892,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -2160,9 +2427,8 @@
   <cols>
     <col min="1" max="1" width="12.1538461538462" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7692307692308" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.4615384615385" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6153846153846" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.4615384615385" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17.4615384615385" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5961538461538" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2175,10 +2441,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2189,15 +2455,14 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="str">
-        <f t="shared" ref="E2:E65" si="0">IF(D2="","",IF(ISNUMBER(SEARCH("B0",D2)),"添加到否定ASIN","添加到否定关键词-精准否定"))</f>
-        <v>添加到否定ASIN</v>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2205,53 +2470,50 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2259,17 +2521,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2277,35 +2538,33 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2315,15 +2574,14 @@
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2333,33 +2591,31 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2369,33 +2625,31 @@
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>42</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2405,15 +2659,14 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2421,17 +2674,16 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2439,17 +2691,16 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2457,35 +2708,33 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>54</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2493,17 +2742,16 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2511,71 +2759,67 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>64</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>68</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2583,35 +2827,33 @@
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>80</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2619,71 +2861,67 @@
         <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>84</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>92</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2691,17 +2929,16 @@
         <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2709,17 +2946,16 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>99</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2727,17 +2963,16 @@
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E32" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2747,15 +2982,14 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2763,17 +2997,16 @@
         <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2781,17 +3014,16 @@
         <v>5</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2799,17 +3031,16 @@
         <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>10</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2817,17 +3048,16 @@
         <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>115</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2835,17 +3065,16 @@
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2853,17 +3082,16 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2871,17 +3099,16 @@
         <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2889,17 +3116,16 @@
         <v>5</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E41" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2907,71 +3133,67 @@
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E42" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E43" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>132</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2981,33 +3203,31 @@
       <c r="B46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E46" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C46" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -3017,15 +3237,14 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3033,17 +3252,16 @@
         <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E49" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3051,17 +3269,16 @@
         <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -3069,17 +3286,16 @@
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E51" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>151</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -3087,35 +3303,33 @@
         <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E53" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>64</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -3123,17 +3337,16 @@
         <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E54" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3143,33 +3356,31 @@
       <c r="B55" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E55" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="D55" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E56" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3179,51 +3390,48 @@
       <c r="B57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+      <c r="C57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E58" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E59" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>68</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3231,35 +3439,33 @@
         <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>168</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E61" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>92</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3267,35 +3473,33 @@
         <v>5</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E62" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E63" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>178</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3303,35 +3507,33 @@
         <v>5</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E64" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>84</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E65" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>添加到否定ASIN</v>
+        <v>183</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3339,17 +3541,16 @@
         <v>5</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E66" s="1" t="str">
-        <f t="shared" ref="E66:E129" si="1">IF(D66="","",IF(ISNUMBER(SEARCH("B0",D66)),"添加到否定ASIN","添加到否定关键词-精准否定"))</f>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3359,33 +3560,31 @@
       <c r="B67" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E67" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C67" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E68" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>190</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3393,17 +3592,16 @@
         <v>5</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E69" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>115</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3411,35 +3609,33 @@
         <v>5</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E70" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E71" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>196</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3447,71 +3643,67 @@
         <v>5</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E72" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E73" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>202</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E74" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E75" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>209</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3519,17 +3711,16 @@
         <v>5</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E76" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3537,89 +3728,84 @@
         <v>5</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E77" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E78" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>178</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E79" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E80" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E81" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>224</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3627,17 +3813,16 @@
         <v>5</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E82" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3645,17 +3830,16 @@
         <v>5</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E83" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3663,17 +3847,16 @@
         <v>5</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E84" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>10</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3681,35 +3864,33 @@
         <v>5</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E85" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E86" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3719,15 +3900,14 @@
       <c r="B87" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E87" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C87" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3735,17 +3915,16 @@
         <v>5</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E88" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3753,17 +3932,16 @@
         <v>5</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E89" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3773,15 +3951,14 @@
       <c r="B90" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E90" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="D90" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3789,17 +3966,16 @@
         <v>5</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E91" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3807,17 +3983,16 @@
         <v>5</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E92" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>246</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3825,17 +4000,16 @@
         <v>5</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E93" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3843,35 +4017,33 @@
         <v>5</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E94" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E95" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3879,17 +4051,16 @@
         <v>5</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E96" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3897,17 +4068,16 @@
         <v>5</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E97" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3917,15 +4087,14 @@
       <c r="B98" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E98" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C98" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3935,15 +4104,14 @@
       <c r="B99" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E99" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C99" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3951,17 +4119,16 @@
         <v>5</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E100" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>10</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3969,17 +4136,16 @@
         <v>5</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E101" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3987,35 +4153,33 @@
         <v>5</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E102" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>84</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E103" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>132</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4023,35 +4187,33 @@
         <v>5</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E104" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E105" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>42</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4059,17 +4221,16 @@
         <v>5</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E106" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -4077,17 +4238,16 @@
         <v>5</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E107" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -4095,17 +4255,16 @@
         <v>5</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C108" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -4113,17 +4272,16 @@
         <v>5</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E109" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -4131,53 +4289,50 @@
         <v>5</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E110" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E111" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>64</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E112" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>183</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -4185,17 +4340,16 @@
         <v>5</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E113" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4203,71 +4357,67 @@
         <v>5</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E114" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E115" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E116" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>64</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E117" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4275,35 +4425,33 @@
         <v>5</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E118" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>115</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E119" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4311,35 +4459,33 @@
         <v>5</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E120" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E121" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>132</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4347,17 +4493,16 @@
         <v>5</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E122" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4367,15 +4512,14 @@
       <c r="B123" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E123" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C123" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4383,17 +4527,16 @@
         <v>5</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E124" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -4403,51 +4546,48 @@
       <c r="B125" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C125" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E125" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+      <c r="C125" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E126" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>202</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E127" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4455,17 +4595,16 @@
         <v>5</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E128" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>84</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -4473,17 +4612,16 @@
         <v>5</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E129" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4491,17 +4629,16 @@
         <v>5</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E130" s="1" t="str">
-        <f t="shared" ref="E130:E193" si="2">IF(D130="","",IF(ISNUMBER(SEARCH("B0",D130)),"添加到否定ASIN","添加到否定关键词-精准否定"))</f>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -4509,17 +4646,16 @@
         <v>5</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E131" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -4529,15 +4665,14 @@
       <c r="B132" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C132" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E132" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C132" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -4547,15 +4682,14 @@
       <c r="B133" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C133" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E133" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C133" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -4563,35 +4697,33 @@
         <v>5</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E134" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E135" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>190</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -4599,35 +4731,33 @@
         <v>5</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E136" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>10</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="E137" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>202</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -4635,17 +4765,16 @@
         <v>5</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E138" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>84</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4653,17 +4782,16 @@
         <v>5</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E139" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -4673,33 +4801,31 @@
       <c r="B140" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C140" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E140" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C140" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E141" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>64</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -4707,17 +4833,16 @@
         <v>5</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E142" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -4725,17 +4850,16 @@
         <v>5</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E143" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -4745,15 +4869,14 @@
       <c r="B144" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C144" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E144" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C144" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4761,17 +4884,16 @@
         <v>5</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E145" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>115</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4779,89 +4901,84 @@
         <v>5</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E146" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>335</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E147" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>178</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E148" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>54</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E149" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>202</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E150" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4869,35 +4986,33 @@
         <v>5</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E151" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E152" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>68</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4905,53 +5020,50 @@
         <v>5</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E153" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E154" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E155" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -4961,51 +5073,48 @@
       <c r="B156" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E156" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C156" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E157" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>132</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E158" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>132</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -5013,17 +5122,16 @@
         <v>5</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E159" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>115</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -5031,17 +5139,16 @@
         <v>5</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E160" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -5051,51 +5158,48 @@
       <c r="B161" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C161" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="E161" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C161" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E162" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E163" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -5103,35 +5207,33 @@
         <v>5</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E164" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>168</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E165" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>15</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -5139,17 +5241,16 @@
         <v>5</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C166" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E166" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -5157,17 +5258,16 @@
         <v>5</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E167" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>10</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -5175,17 +5275,16 @@
         <v>5</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C168" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E168" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -5193,17 +5292,16 @@
         <v>5</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E169" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -5211,17 +5309,16 @@
         <v>5</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E170" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -5229,17 +5326,16 @@
         <v>5</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E171" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -5247,17 +5343,16 @@
         <v>5</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="E172" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -5267,15 +5362,14 @@
       <c r="B173" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C173" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E173" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C173" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -5283,35 +5377,33 @@
         <v>5</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E174" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E175" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -5319,17 +5411,16 @@
         <v>5</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E176" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>75</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -5337,17 +5428,16 @@
         <v>5</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E177" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -5355,35 +5445,33 @@
         <v>5</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C178" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E178" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E179" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>64</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -5393,15 +5481,14 @@
       <c r="B180" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C180" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E180" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C180" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -5409,17 +5496,16 @@
         <v>5</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E181" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -5427,17 +5513,16 @@
         <v>5</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E182" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -5445,17 +5530,16 @@
         <v>5</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E183" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -5463,53 +5547,50 @@
         <v>5</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E184" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E185" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>42</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E186" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -5517,17 +5598,16 @@
         <v>5</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E187" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -5535,35 +5615,33 @@
         <v>5</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E188" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>120</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E189" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>19</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -5571,35 +5649,33 @@
         <v>5</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E190" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E191" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>28</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -5607,17 +5683,16 @@
         <v>5</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E192" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+        <v>23</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -5625,17 +5700,16 @@
         <v>5</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C193" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E193" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>添加到否定ASIN</v>
+      <c r="C193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
